--- a/option-portfolio-tracker/opt_hist_updated.xlsx
+++ b/option-portfolio-tracker/opt_hist_updated.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\python_project\boors\Ekhtiyar\option-portfolio-tracker\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CADBFC-67DD-46F0-8A91-96C95E1FDCCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -112,8 +123,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,6 +187,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -222,7 +241,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -254,9 +273,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -288,6 +325,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -463,16 +518,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +539,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -488,7 +547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -496,7 +555,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -504,7 +563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -512,7 +571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -520,7 +579,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -528,7 +587,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -536,7 +595,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -544,7 +603,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -552,15 +611,15 @@
         <v>42828</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>0.14699999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -568,7 +627,7 @@
         <v>4602</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -576,7 +635,7 @@
         <v>42832</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -584,55 +643,55 @@
         <v>37734</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0.167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0.926</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>0.92600000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>-0.119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>-0.11899999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B20">
-        <v>-0.057</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>-5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>-0.509</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>-0.50900000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -640,23 +699,23 @@
         <v>0.3251</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0.1387</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>0.13869999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B24">
-        <v>3.8582</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>3.8582000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -664,7 +723,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -672,7 +731,7 @@
         <v>42828000</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -680,7 +739,7 @@
         <v>7152276</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
